--- a/DataTables/Datas/#VSStage.xlsx
+++ b/DataTables/Datas/#VSStage.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,11 @@
           <t>enemyId</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>damageTextEntityId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +514,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -554,6 +564,11 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>本关刷的敌人id(#VSEnemy)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>伤害飘字实体id(#Entity)</t>
         </is>
       </c>
     </row>
@@ -583,6 +598,9 @@
       </c>
       <c r="I4" t="n">
         <v>201001</v>
+      </c>
+      <c r="J4" t="n">
+        <v>500002</v>
       </c>
     </row>
   </sheetData>
